--- a/Excel/EquipRefineConfig.xlsx
+++ b/Excel/EquipRefineConfig.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowHeight="17680"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1012,8 +1012,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C1:H19"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1" outlineLevelCol="7"/>
+  <dimension ref="C1:G29"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="2" width="9" style="1"/>
     <col min="3" max="5" width="8.75" style="1" customWidth="1"/>
@@ -1217,7 +1217,7 @@
         <v>100000</v>
       </c>
     </row>
-    <row r="14" customHeight="1" spans="3:8">
+    <row r="14" customHeight="1" spans="3:7">
       <c r="C14" s="2">
         <v>9</v>
       </c>
@@ -1233,7 +1233,6 @@
       <c r="G14" s="2">
         <v>200000</v>
       </c>
-      <c r="H14" s="2"/>
     </row>
     <row r="15" customHeight="1" spans="3:7">
       <c r="C15" s="2">
@@ -1311,7 +1310,7 @@
         <v>501</v>
       </c>
       <c r="E19" s="1">
-        <v>501</v>
+        <v>550</v>
       </c>
       <c r="F19" s="1">
         <v>57000000</v>
@@ -1320,9 +1319,186 @@
         <v>700000</v>
       </c>
     </row>
+    <row r="20" customHeight="1" spans="3:7">
+      <c r="C20" s="1">
+        <v>15</v>
+      </c>
+      <c r="D20" s="1">
+        <v>551</v>
+      </c>
+      <c r="E20" s="1">
+        <v>600</v>
+      </c>
+      <c r="F20" s="1">
+        <v>92000000</v>
+      </c>
+      <c r="G20" s="1">
+        <v>800000</v>
+      </c>
+    </row>
+    <row r="21" customHeight="1" spans="3:7">
+      <c r="C21" s="1">
+        <v>16</v>
+      </c>
+      <c r="D21" s="1">
+        <v>601</v>
+      </c>
+      <c r="E21" s="1">
+        <v>650</v>
+      </c>
+      <c r="F21" s="1">
+        <v>132000000</v>
+      </c>
+      <c r="G21" s="1">
+        <v>900000</v>
+      </c>
+    </row>
+    <row r="22" customHeight="1" spans="3:7">
+      <c r="C22" s="1">
+        <v>17</v>
+      </c>
+      <c r="D22" s="1">
+        <v>651</v>
+      </c>
+      <c r="E22" s="1">
+        <v>700</v>
+      </c>
+      <c r="F22" s="1">
+        <v>177000000</v>
+      </c>
+      <c r="G22" s="1">
+        <v>1000000</v>
+      </c>
+    </row>
+    <row r="23" customHeight="1" spans="3:7">
+      <c r="C23" s="1">
+        <v>18</v>
+      </c>
+      <c r="D23" s="1">
+        <v>701</v>
+      </c>
+      <c r="E23" s="1">
+        <v>750</v>
+      </c>
+      <c r="F23" s="1">
+        <f t="shared" ref="F23:F27" si="0">F22+G22*50</f>
+        <v>227000000</v>
+      </c>
+      <c r="G23" s="1">
+        <v>1500000</v>
+      </c>
+    </row>
+    <row r="24" customHeight="1" spans="3:7">
+      <c r="C24" s="1">
+        <v>19</v>
+      </c>
+      <c r="D24" s="1">
+        <v>751</v>
+      </c>
+      <c r="E24" s="1">
+        <v>800</v>
+      </c>
+      <c r="F24" s="1">
+        <f t="shared" si="0"/>
+        <v>302000000</v>
+      </c>
+      <c r="G24" s="1">
+        <v>2000000</v>
+      </c>
+    </row>
+    <row r="25" customHeight="1" spans="3:7">
+      <c r="C25" s="1">
+        <v>20</v>
+      </c>
+      <c r="D25" s="1">
+        <v>801</v>
+      </c>
+      <c r="E25" s="1">
+        <v>900</v>
+      </c>
+      <c r="F25" s="1">
+        <f t="shared" si="0"/>
+        <v>402000000</v>
+      </c>
+      <c r="G25" s="1">
+        <v>3000000</v>
+      </c>
+    </row>
+    <row r="26" customHeight="1" spans="3:7">
+      <c r="C26" s="1">
+        <v>21</v>
+      </c>
+      <c r="D26" s="1">
+        <v>901</v>
+      </c>
+      <c r="E26" s="1">
+        <v>1000</v>
+      </c>
+      <c r="F26" s="1">
+        <f t="shared" ref="F26:F28" si="1">F25+G25*100</f>
+        <v>702000000</v>
+      </c>
+      <c r="G26" s="1">
+        <v>4000000</v>
+      </c>
+    </row>
+    <row r="27" customHeight="1" spans="3:7">
+      <c r="C27" s="1">
+        <v>22</v>
+      </c>
+      <c r="D27" s="1">
+        <v>1001</v>
+      </c>
+      <c r="E27" s="1">
+        <v>1200</v>
+      </c>
+      <c r="F27" s="1">
+        <f t="shared" ref="F27:F30" si="2">F26+G26*200</f>
+        <v>1502000000</v>
+      </c>
+      <c r="G27" s="1">
+        <v>6000000</v>
+      </c>
+    </row>
+    <row r="28" customHeight="1" spans="3:7">
+      <c r="C28" s="1">
+        <v>23</v>
+      </c>
+      <c r="D28" s="1">
+        <v>1201</v>
+      </c>
+      <c r="E28" s="1">
+        <v>1400</v>
+      </c>
+      <c r="F28" s="1">
+        <f t="shared" si="2"/>
+        <v>2702000000</v>
+      </c>
+      <c r="G28" s="1">
+        <v>8000000</v>
+      </c>
+    </row>
+    <row r="29" customHeight="1" spans="3:7">
+      <c r="C29" s="1">
+        <v>24</v>
+      </c>
+      <c r="D29" s="1">
+        <v>1401</v>
+      </c>
+      <c r="E29" s="1">
+        <v>1700</v>
+      </c>
+      <c r="F29" s="1">
+        <f t="shared" si="2"/>
+        <v>4302000000</v>
+      </c>
+      <c r="G29" s="1">
+        <v>10000000</v>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C2 D2 E2 F2 G2 C3 D3 E3 F3 G3 D4 E4 F4 G4 D5 E5 F5 G5 C4:C5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C2:G5" errorStyle="warning">
       <formula1>COUNTIF($C:$C,C2)&lt;2</formula1>
     </dataValidation>
   </dataValidations>

--- a/Excel/EquipRefineConfig.xlsx
+++ b/Excel/EquipRefineConfig.xlsx
@@ -38,7 +38,7 @@
     <t>EndLevel</t>
   </si>
   <si>
-    <t>BaseFee</t>
+    <t>Fee</t>
   </si>
   <si>
     <t>RiseFee</t>
@@ -63,7 +63,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -82,6 +82,12 @@
       <sz val="9"/>
       <color theme="1"/>
       <name val="等线"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
     <font>
@@ -553,137 +559,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -693,6 +699,7 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1012,7 +1019,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C1:G29"/>
+  <dimension ref="C1:G16"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="2" width="9" style="1"/>
@@ -1082,423 +1089,145 @@
       </c>
     </row>
     <row r="6" customHeight="1" spans="3:7">
-      <c r="C6" s="2">
+      <c r="C6" s="5">
         <v>1</v>
       </c>
-      <c r="D6" s="2">
+      <c r="D6" s="5">
         <v>1</v>
       </c>
-      <c r="E6" s="2">
-        <v>49</v>
-      </c>
-      <c r="F6" s="2">
-        <v>0</v>
-      </c>
-      <c r="G6" s="2">
+      <c r="E6" s="5">
         <v>10</v>
       </c>
+      <c r="F6" s="5">
+        <v>10</v>
+      </c>
+      <c r="G6" s="5">
+        <v>10</v>
+      </c>
     </row>
     <row r="7" customHeight="1" spans="3:7">
-      <c r="C7" s="2">
+      <c r="C7" s="5">
         <v>2</v>
       </c>
-      <c r="D7" s="2">
+      <c r="D7" s="5">
+        <f t="shared" ref="D7:D11" si="0">E6+1</f>
+        <v>11</v>
+      </c>
+      <c r="E7" s="5">
+        <v>20</v>
+      </c>
+      <c r="F7" s="5">
+        <v>100</v>
+      </c>
+      <c r="G7" s="5">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="8" customHeight="1" spans="3:7">
+      <c r="C8" s="5">
+        <v>3</v>
+      </c>
+      <c r="D8" s="5">
+        <f t="shared" si="0"/>
+        <v>21</v>
+      </c>
+      <c r="E8" s="5">
+        <v>30</v>
+      </c>
+      <c r="F8" s="5">
+        <v>1000</v>
+      </c>
+      <c r="G8" s="5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="9" customHeight="1" spans="3:7">
+      <c r="C9" s="5">
+        <v>4</v>
+      </c>
+      <c r="D9" s="5">
+        <f t="shared" si="0"/>
+        <v>31</v>
+      </c>
+      <c r="E9" s="5">
+        <v>40</v>
+      </c>
+      <c r="F9" s="5">
+        <v>3000</v>
+      </c>
+      <c r="G9" s="5">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="10" customHeight="1" spans="3:7">
+      <c r="C10" s="5">
+        <v>5</v>
+      </c>
+      <c r="D10" s="5">
+        <f t="shared" si="0"/>
+        <v>41</v>
+      </c>
+      <c r="E10" s="5">
         <v>50</v>
       </c>
-      <c r="E7" s="2">
-        <v>99</v>
-      </c>
-      <c r="F7" s="2">
-        <v>0</v>
-      </c>
-      <c r="G7" s="2">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="8" customHeight="1" spans="3:7">
-      <c r="C8" s="2">
-        <v>3</v>
-      </c>
-      <c r="D8" s="2">
-        <v>100</v>
-      </c>
-      <c r="E8" s="2">
-        <v>149</v>
-      </c>
-      <c r="F8" s="2">
-        <v>0</v>
-      </c>
-      <c r="G8" s="2">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="9" customHeight="1" spans="3:7">
-      <c r="C9" s="2">
-        <v>4</v>
-      </c>
-      <c r="D9" s="2">
-        <v>150</v>
-      </c>
-      <c r="E9" s="2">
-        <v>199</v>
-      </c>
-      <c r="F9" s="2">
-        <v>0</v>
-      </c>
-      <c r="G9" s="2">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="10" customHeight="1" spans="3:7">
-      <c r="C10" s="2">
-        <v>5</v>
-      </c>
-      <c r="D10" s="2">
-        <v>200</v>
-      </c>
-      <c r="E10" s="2">
-        <v>249</v>
-      </c>
-      <c r="F10" s="2">
-        <v>0</v>
-      </c>
-      <c r="G10" s="2">
-        <v>50</v>
+      <c r="F10" s="5">
+        <v>6000</v>
+      </c>
+      <c r="G10" s="5">
+        <v>400</v>
       </c>
     </row>
     <row r="11" customHeight="1" spans="3:7">
-      <c r="C11" s="2">
+      <c r="C11" s="5">
         <v>6</v>
       </c>
-      <c r="D11" s="2">
-        <v>250</v>
-      </c>
-      <c r="E11" s="2">
-        <v>299</v>
-      </c>
-      <c r="F11" s="2">
-        <v>0</v>
-      </c>
-      <c r="G11" s="2">
+      <c r="D11" s="5">
+        <f t="shared" si="0"/>
+        <v>51</v>
+      </c>
+      <c r="E11" s="5">
         <v>60</v>
       </c>
+      <c r="F11" s="5">
+        <v>10000</v>
+      </c>
+      <c r="G11" s="5">
+        <v>500</v>
+      </c>
     </row>
     <row r="12" customHeight="1" spans="3:7">
-      <c r="C12" s="2">
-        <v>7</v>
-      </c>
-      <c r="D12" s="2">
-        <v>300</v>
-      </c>
-      <c r="E12" s="2">
-        <v>349</v>
-      </c>
-      <c r="F12" s="2">
-        <v>0</v>
-      </c>
-      <c r="G12" s="2">
-        <v>70</v>
-      </c>
+      <c r="C12" s="2"/>
+      <c r="D12" s="2"/>
+      <c r="E12" s="2"/>
+      <c r="F12" s="2"/>
+      <c r="G12" s="2"/>
     </row>
     <row r="13" customHeight="1" spans="3:7">
-      <c r="C13" s="2">
-        <v>8</v>
-      </c>
-      <c r="D13" s="2">
-        <v>350</v>
-      </c>
-      <c r="E13" s="2">
-        <v>375</v>
-      </c>
-      <c r="F13" s="2">
-        <v>4400000</v>
-      </c>
-      <c r="G13" s="2">
-        <v>100000</v>
-      </c>
+      <c r="C13" s="2"/>
+      <c r="D13" s="2"/>
+      <c r="E13" s="2"/>
+      <c r="F13" s="2"/>
+      <c r="G13" s="2"/>
     </row>
     <row r="14" customHeight="1" spans="3:7">
-      <c r="C14" s="2">
-        <v>9</v>
-      </c>
-      <c r="D14" s="2">
-        <v>376</v>
-      </c>
-      <c r="E14" s="2">
-        <v>400</v>
-      </c>
-      <c r="F14" s="2">
-        <v>7000000</v>
-      </c>
-      <c r="G14" s="2">
-        <v>200000</v>
-      </c>
+      <c r="C14" s="2"/>
+      <c r="D14" s="2"/>
+      <c r="E14" s="2"/>
+      <c r="F14" s="2"/>
+      <c r="G14" s="2"/>
     </row>
     <row r="15" customHeight="1" spans="3:7">
-      <c r="C15" s="2">
-        <v>10</v>
-      </c>
-      <c r="D15" s="1">
-        <v>401</v>
-      </c>
-      <c r="E15" s="1">
-        <v>425</v>
-      </c>
-      <c r="F15" s="2">
-        <v>12000000</v>
-      </c>
-      <c r="G15" s="1">
-        <v>300000</v>
-      </c>
+      <c r="C15" s="2"/>
+      <c r="D15" s="1"/>
+      <c r="E15" s="1"/>
+      <c r="F15" s="2"/>
     </row>
     <row r="16" customHeight="1" spans="3:7">
-      <c r="C16" s="2">
-        <v>11</v>
-      </c>
-      <c r="D16" s="1">
-        <v>426</v>
-      </c>
-      <c r="E16" s="1">
-        <v>450</v>
-      </c>
-      <c r="F16" s="1">
-        <v>19500000</v>
-      </c>
-      <c r="G16" s="1">
-        <v>400000</v>
-      </c>
-    </row>
-    <row r="17" customHeight="1" spans="3:7">
-      <c r="C17" s="1">
-        <v>12</v>
-      </c>
-      <c r="D17" s="1">
-        <v>451</v>
-      </c>
-      <c r="E17" s="1">
-        <v>475</v>
-      </c>
-      <c r="F17" s="1">
-        <v>29500000</v>
-      </c>
-      <c r="G17" s="1">
-        <v>500000</v>
-      </c>
-    </row>
-    <row r="18" customHeight="1" spans="3:7">
-      <c r="C18" s="1">
-        <v>13</v>
-      </c>
-      <c r="D18" s="1">
-        <v>476</v>
-      </c>
-      <c r="E18" s="1">
-        <v>500</v>
-      </c>
-      <c r="F18" s="1">
-        <v>42000000</v>
-      </c>
-      <c r="G18" s="1">
-        <v>600000</v>
-      </c>
-    </row>
-    <row r="19" customHeight="1" spans="3:7">
-      <c r="C19" s="1">
-        <v>14</v>
-      </c>
-      <c r="D19" s="1">
-        <v>501</v>
-      </c>
-      <c r="E19" s="1">
-        <v>550</v>
-      </c>
-      <c r="F19" s="1">
-        <v>57000000</v>
-      </c>
-      <c r="G19" s="1">
-        <v>700000</v>
-      </c>
-    </row>
-    <row r="20" customHeight="1" spans="3:7">
-      <c r="C20" s="1">
-        <v>15</v>
-      </c>
-      <c r="D20" s="1">
-        <v>551</v>
-      </c>
-      <c r="E20" s="1">
-        <v>600</v>
-      </c>
-      <c r="F20" s="1">
-        <v>92000000</v>
-      </c>
-      <c r="G20" s="1">
-        <v>800000</v>
-      </c>
-    </row>
-    <row r="21" customHeight="1" spans="3:7">
-      <c r="C21" s="1">
-        <v>16</v>
-      </c>
-      <c r="D21" s="1">
-        <v>601</v>
-      </c>
-      <c r="E21" s="1">
-        <v>650</v>
-      </c>
-      <c r="F21" s="1">
-        <v>132000000</v>
-      </c>
-      <c r="G21" s="1">
-        <v>900000</v>
-      </c>
-    </row>
-    <row r="22" customHeight="1" spans="3:7">
-      <c r="C22" s="1">
-        <v>17</v>
-      </c>
-      <c r="D22" s="1">
-        <v>651</v>
-      </c>
-      <c r="E22" s="1">
-        <v>700</v>
-      </c>
-      <c r="F22" s="1">
-        <v>177000000</v>
-      </c>
-      <c r="G22" s="1">
-        <v>1000000</v>
-      </c>
-    </row>
-    <row r="23" customHeight="1" spans="3:7">
-      <c r="C23" s="1">
-        <v>18</v>
-      </c>
-      <c r="D23" s="1">
-        <v>701</v>
-      </c>
-      <c r="E23" s="1">
-        <v>750</v>
-      </c>
-      <c r="F23" s="1">
-        <f t="shared" ref="F23:F27" si="0">F22+G22*50</f>
-        <v>227000000</v>
-      </c>
-      <c r="G23" s="1">
-        <v>1500000</v>
-      </c>
-    </row>
-    <row r="24" customHeight="1" spans="3:7">
-      <c r="C24" s="1">
-        <v>19</v>
-      </c>
-      <c r="D24" s="1">
-        <v>751</v>
-      </c>
-      <c r="E24" s="1">
-        <v>800</v>
-      </c>
-      <c r="F24" s="1">
-        <f t="shared" si="0"/>
-        <v>302000000</v>
-      </c>
-      <c r="G24" s="1">
-        <v>2000000</v>
-      </c>
-    </row>
-    <row r="25" customHeight="1" spans="3:7">
-      <c r="C25" s="1">
-        <v>20</v>
-      </c>
-      <c r="D25" s="1">
-        <v>801</v>
-      </c>
-      <c r="E25" s="1">
-        <v>900</v>
-      </c>
-      <c r="F25" s="1">
-        <f t="shared" si="0"/>
-        <v>402000000</v>
-      </c>
-      <c r="G25" s="1">
-        <v>3000000</v>
-      </c>
-    </row>
-    <row r="26" customHeight="1" spans="3:7">
-      <c r="C26" s="1">
-        <v>21</v>
-      </c>
-      <c r="D26" s="1">
-        <v>901</v>
-      </c>
-      <c r="E26" s="1">
-        <v>1000</v>
-      </c>
-      <c r="F26" s="1">
-        <f t="shared" ref="F26:F28" si="1">F25+G25*100</f>
-        <v>702000000</v>
-      </c>
-      <c r="G26" s="1">
-        <v>4000000</v>
-      </c>
-    </row>
-    <row r="27" customHeight="1" spans="3:7">
-      <c r="C27" s="1">
-        <v>22</v>
-      </c>
-      <c r="D27" s="1">
-        <v>1001</v>
-      </c>
-      <c r="E27" s="1">
-        <v>1200</v>
-      </c>
-      <c r="F27" s="1">
-        <f t="shared" ref="F27:F30" si="2">F26+G26*200</f>
-        <v>1502000000</v>
-      </c>
-      <c r="G27" s="1">
-        <v>6000000</v>
-      </c>
-    </row>
-    <row r="28" customHeight="1" spans="3:7">
-      <c r="C28" s="1">
-        <v>23</v>
-      </c>
-      <c r="D28" s="1">
-        <v>1201</v>
-      </c>
-      <c r="E28" s="1">
-        <v>1400</v>
-      </c>
-      <c r="F28" s="1">
-        <f t="shared" si="2"/>
-        <v>2702000000</v>
-      </c>
-      <c r="G28" s="1">
-        <v>8000000</v>
-      </c>
-    </row>
-    <row r="29" customHeight="1" spans="3:7">
-      <c r="C29" s="1">
-        <v>24</v>
-      </c>
-      <c r="D29" s="1">
-        <v>1401</v>
-      </c>
-      <c r="E29" s="1">
-        <v>1700</v>
-      </c>
-      <c r="F29" s="1">
-        <f t="shared" si="2"/>
-        <v>4302000000</v>
-      </c>
-      <c r="G29" s="1">
-        <v>10000000</v>
-      </c>
+      <c r="C16" s="2"/>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C2:G5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C4:E4 F4 G4 C5:G5 C2:G3" errorStyle="warning">
       <formula1>COUNTIF($C:$C,C2)&lt;2</formula1>
     </dataValidation>
   </dataValidations>

--- a/Excel/EquipRefineConfig.xlsx
+++ b/Excel/EquipRefineConfig.xlsx
@@ -27,21 +27,36 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="43">
+  <si>
+    <t>#</t>
+  </si>
   <si>
     <t>_id</t>
   </si>
   <si>
-    <t>StartLevel</t>
-  </si>
-  <si>
-    <t>EndLevel</t>
-  </si>
-  <si>
-    <t>Fee</t>
-  </si>
-  <si>
-    <t>RiseFee</t>
+    <t>Position</t>
+  </si>
+  <si>
+    <t>AtrList</t>
+  </si>
+  <si>
+    <t>AtrVueList</t>
+  </si>
+  <si>
+    <t>RequireLevel</t>
+  </si>
+  <si>
+    <t>FeeBase</t>
+  </si>
+  <si>
+    <t>SpeAtrList</t>
+  </si>
+  <si>
+    <t>SpeVueList</t>
+  </si>
+  <si>
+    <t>SpeLevel</t>
   </si>
   <si>
     <t>Id</t>
@@ -50,7 +65,97 @@
     <t>int</t>
   </si>
   <si>
-    <t>long</t>
+    <t>int[]</t>
+  </si>
+  <si>
+    <t>long[]</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>20001,20002,20003</t>
+  </si>
+  <si>
+    <t>1,1,1</t>
+  </si>
+  <si>
+    <t>0,20,40,60</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>30</t>
+  </si>
+  <si>
+    <t>幸运</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>诅咒</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>命中</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>闪避</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>攻速</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>22</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>爆伤</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>25</t>
+  </si>
+  <si>
+    <t>抗暴率</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>移速</t>
   </si>
 </sst>
 </file>
@@ -63,13 +168,19 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="24">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
@@ -81,13 +192,14 @@
       <b/>
       <sz val="9"/>
       <color theme="1"/>
-      <name val="等线"/>
+      <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <color theme="1"/>
-      <name val="微软雅黑"/>
+      <name val="等线"/>
       <charset val="134"/>
     </font>
     <font>
@@ -559,147 +671,157 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1019,215 +1141,515 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C1:G16"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1" outlineLevelCol="6"/>
+  <dimension ref="A1:XFD16"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="2" width="9" style="1"/>
-    <col min="3" max="5" width="8.75" style="1" customWidth="1"/>
-    <col min="6" max="7" width="13.625" style="1" customWidth="1"/>
-    <col min="8" max="16381" width="9" style="1"/>
-    <col min="16382" max="16384" width="9" style="2"/>
+    <col min="3" max="3" width="10.1666666666667" style="1" customWidth="1"/>
+    <col min="4" max="4" width="8.75" style="1" customWidth="1"/>
+    <col min="5" max="5" width="22.5833333333333" style="2" customWidth="1"/>
+    <col min="6" max="6" width="22.25" style="2" customWidth="1"/>
+    <col min="7" max="7" width="19.9166666666667" style="3" customWidth="1"/>
+    <col min="8" max="8" width="15.0833333333333" style="3" customWidth="1"/>
+    <col min="9" max="9" width="21.5" style="2" customWidth="1"/>
+    <col min="10" max="10" width="20.6666666666667" style="2" customWidth="1"/>
+    <col min="11" max="11" width="19.8333333333333" style="3" customWidth="1"/>
+    <col min="12" max="12" width="10.5" style="1" customWidth="1"/>
+    <col min="13" max="16381" width="9" style="1"/>
+    <col min="16384" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" customHeight="1"/>
-    <row r="2" s="1" customFormat="1" customHeight="1" spans="3:7">
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
+    <row r="1" s="1" customFormat="1" ht="13" spans="1:12 16382:16384">
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="3"/>
+      <c r="H1" s="3"/>
+      <c r="I1" s="2"/>
+      <c r="J1" s="2"/>
+      <c r="K1" s="3"/>
+      <c r="L1" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" s="1" customFormat="1" ht="13" spans="1:12 16382:16384">
+      <c r="C2" s="5"/>
+      <c r="D2" s="5"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
       <c r="G2" s="3"/>
+      <c r="H2" s="3"/>
+      <c r="I2" s="2"/>
+      <c r="J2" s="2"/>
+      <c r="K2" s="3"/>
+      <c r="L2" s="1" t="s">
+        <v>0</v>
+      </c>
     </row>
-    <row r="3" s="1" customFormat="1" customHeight="1" spans="3:7">
-      <c r="C3" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="D3" s="4" t="s">
+    <row r="3" s="1" customFormat="1" ht="13.5" spans="1:12 16382:16384">
+      <c r="C3" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="D3" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="E3" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="G3" s="4" t="s">
+      <c r="F3" s="7" t="s">
         <v>4</v>
       </c>
+      <c r="G3" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="H3" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="I3" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="J3" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="K3" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="L3" s="8"/>
     </row>
-    <row r="4" s="1" customFormat="1" customHeight="1" spans="3:7">
-      <c r="C4" s="4" t="s">
+    <row r="4" s="1" customFormat="1" ht="13.5" spans="1:12 16382:16384">
+      <c r="C4" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="F4" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="G4" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="H4" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="I4" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="J4" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="K4" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="L4" s="8"/>
+    </row>
+    <row r="5" s="1" customFormat="1" ht="13.5" spans="1:12 16382:16384">
+      <c r="C5" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E5" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F5" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="G5" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="H5" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="I5" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="J5" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="K5" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="L5" s="8"/>
+    </row>
+    <row r="6" customFormat="1" ht="24" customHeight="1" spans="1:12 16382:16384">
+      <c r="A6" s="1"/>
+      <c r="B6" s="1"/>
+      <c r="C6" t="s">
+        <v>14</v>
+      </c>
+      <c r="D6" t="s">
+        <v>14</v>
+      </c>
+      <c r="E6" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="F6" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="G6" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="H6" s="9">
+        <v>2</v>
+      </c>
+      <c r="I6" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="J6" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="K6" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="L6" t="s">
+        <v>20</v>
+      </c>
+      <c r="XFB6" s="4"/>
+      <c r="XFC6" s="4"/>
+    </row>
+    <row r="7" customFormat="1" ht="24" customHeight="1" spans="1:12 16382:16384">
+      <c r="A7" s="1"/>
+      <c r="B7" s="1"/>
+      <c r="C7" t="s">
+        <v>21</v>
+      </c>
+      <c r="D7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E7" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="F7" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="G7" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="H7" s="9">
+        <v>2</v>
+      </c>
+      <c r="I7" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="J7" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="K7" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="L7" t="s">
+        <v>23</v>
+      </c>
+      <c r="XFB7" s="4"/>
+      <c r="XFC7" s="4"/>
+    </row>
+    <row r="8" customFormat="1" ht="24" customHeight="1" spans="1:12 16382:16384">
+      <c r="A8" s="1"/>
+      <c r="B8" s="1"/>
+      <c r="C8" t="s">
+        <v>24</v>
+      </c>
+      <c r="D8" t="s">
+        <v>24</v>
+      </c>
+      <c r="E8" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="F8" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="G8" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="H8" s="9">
         <v>1</v>
       </c>
-      <c r="E4" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="G4" s="4" t="s">
-        <v>4</v>
-      </c>
+      <c r="I8" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="J8" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="K8" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="L8" t="s">
+        <v>27</v>
+      </c>
+      <c r="XFB8" s="4"/>
+      <c r="XFC8" s="4"/>
     </row>
-    <row r="5" s="1" customFormat="1" customHeight="1" spans="3:7">
-      <c r="C5" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="G5" s="4" t="s">
-        <v>7</v>
-      </c>
+    <row r="9" customFormat="1" ht="24" customHeight="1" spans="1:12 16382:16384">
+      <c r="A9" s="1"/>
+      <c r="B9" s="1"/>
+      <c r="C9" t="s">
+        <v>28</v>
+      </c>
+      <c r="D9" t="s">
+        <v>28</v>
+      </c>
+      <c r="E9" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="F9" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="G9" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="H9" s="9">
+        <v>1</v>
+      </c>
+      <c r="I9" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="J9" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="K9" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="L9" t="s">
+        <v>30</v>
+      </c>
+      <c r="XFB9" s="4"/>
+      <c r="XFC9" s="4"/>
     </row>
-    <row r="6" customHeight="1" spans="3:7">
-      <c r="C6" s="5">
+    <row r="10" customFormat="1" ht="24" customHeight="1" spans="1:12 16382:16384">
+      <c r="A10" s="1"/>
+      <c r="B10" s="1"/>
+      <c r="C10" t="s">
+        <v>26</v>
+      </c>
+      <c r="D10" t="s">
+        <v>26</v>
+      </c>
+      <c r="E10" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="F10" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="G10" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="H10" s="9">
         <v>1</v>
       </c>
-      <c r="D6" s="5">
+      <c r="I10" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="J10" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="K10" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="L10" t="s">
+        <v>32</v>
+      </c>
+      <c r="XFB10" s="4"/>
+      <c r="XFC10" s="4"/>
+    </row>
+    <row r="11" customFormat="1" ht="24" customHeight="1" spans="1:12 16382:16384">
+      <c r="A11" s="1"/>
+      <c r="B11" s="1"/>
+      <c r="C11" t="s">
+        <v>33</v>
+      </c>
+      <c r="D11" t="s">
+        <v>33</v>
+      </c>
+      <c r="E11" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="F11" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="G11" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="H11" s="9">
         <v>1</v>
       </c>
-      <c r="E6" s="5">
-        <v>10</v>
-      </c>
-      <c r="F6" s="5">
-        <v>10</v>
-      </c>
-      <c r="G6" s="5">
-        <v>10</v>
-      </c>
+      <c r="I11" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="J11" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="K11" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="L11" t="s">
+        <v>32</v>
+      </c>
+      <c r="XFB11" s="4"/>
+      <c r="XFC11" s="4"/>
     </row>
-    <row r="7" customHeight="1" spans="3:7">
-      <c r="C7" s="5">
-        <v>2</v>
-      </c>
-      <c r="D7" s="5">
-        <f t="shared" ref="D7:D11" si="0">E6+1</f>
-        <v>11</v>
-      </c>
-      <c r="E7" s="5">
-        <v>20</v>
-      </c>
-      <c r="F7" s="5">
-        <v>100</v>
-      </c>
-      <c r="G7" s="5">
-        <v>100</v>
-      </c>
+    <row r="12" customFormat="1" ht="24" customHeight="1" spans="1:12 16382:16384">
+      <c r="A12" s="1"/>
+      <c r="B12" s="1"/>
+      <c r="C12" t="s">
+        <v>18</v>
+      </c>
+      <c r="D12" t="s">
+        <v>18</v>
+      </c>
+      <c r="E12" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="F12" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="G12" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="H12" s="9">
+        <v>1</v>
+      </c>
+      <c r="I12" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="J12" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="K12" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="L12" t="s">
+        <v>36</v>
+      </c>
+      <c r="XFB12" s="4"/>
+      <c r="XFC12" s="4"/>
     </row>
-    <row r="8" customHeight="1" spans="3:7">
-      <c r="C8" s="5">
-        <v>3</v>
-      </c>
-      <c r="D8" s="5">
-        <f t="shared" si="0"/>
-        <v>21</v>
-      </c>
-      <c r="E8" s="5">
-        <v>30</v>
-      </c>
-      <c r="F8" s="5">
-        <v>1000</v>
-      </c>
-      <c r="G8" s="5">
-        <v>200</v>
-      </c>
+    <row r="13" customFormat="1" ht="24" customHeight="1" spans="1:12 16382:16384">
+      <c r="A13" s="1"/>
+      <c r="B13" s="1"/>
+      <c r="C13" t="s">
+        <v>22</v>
+      </c>
+      <c r="D13" t="s">
+        <v>22</v>
+      </c>
+      <c r="E13" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="F13" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="G13" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="H13" s="9">
+        <v>1</v>
+      </c>
+      <c r="I13" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="J13" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="K13" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="L13" t="s">
+        <v>36</v>
+      </c>
+      <c r="XFB13" s="4"/>
+      <c r="XFC13" s="4"/>
     </row>
-    <row r="9" customHeight="1" spans="3:7">
-      <c r="C9" s="5">
-        <v>4</v>
-      </c>
-      <c r="D9" s="5">
-        <f t="shared" si="0"/>
-        <v>31</v>
-      </c>
-      <c r="E9" s="5">
+    <row r="14" customFormat="1" ht="24" customHeight="1" spans="1:12 16382:16384">
+      <c r="A14" s="1"/>
+      <c r="B14" s="1"/>
+      <c r="C14" t="s">
+        <v>37</v>
+      </c>
+      <c r="D14" t="s">
+        <v>37</v>
+      </c>
+      <c r="E14" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="F14" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="G14" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="H14" s="9">
+        <v>1</v>
+      </c>
+      <c r="I14" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="J14" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="K14" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="L14" t="s">
+        <v>39</v>
+      </c>
+      <c r="XFB14" s="4"/>
+      <c r="XFC14" s="4"/>
+    </row>
+    <row r="15" customFormat="1" ht="24" customHeight="1" spans="1:12 16382:16384">
+      <c r="A15" s="1"/>
+      <c r="B15" s="1"/>
+      <c r="C15" t="s">
         <v>40</v>
       </c>
-      <c r="F9" s="5">
-        <v>3000</v>
-      </c>
-      <c r="G9" s="5">
-        <v>300</v>
-      </c>
+      <c r="D15" t="s">
+        <v>40</v>
+      </c>
+      <c r="E15" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="F15" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="G15" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="H15" s="9">
+        <v>1</v>
+      </c>
+      <c r="I15" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="J15" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="K15" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="L15" t="s">
+        <v>42</v>
+      </c>
+      <c r="XFB15" s="4"/>
+      <c r="XFC15" s="4"/>
     </row>
-    <row r="10" customHeight="1" spans="3:7">
-      <c r="C10" s="5">
-        <v>5</v>
-      </c>
-      <c r="D10" s="5">
-        <f t="shared" si="0"/>
-        <v>41</v>
-      </c>
-      <c r="E10" s="5">
-        <v>50</v>
-      </c>
-      <c r="F10" s="5">
-        <v>6000</v>
-      </c>
-      <c r="G10" s="5">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="11" customHeight="1" spans="3:7">
-      <c r="C11" s="5">
-        <v>6</v>
-      </c>
-      <c r="D11" s="5">
-        <f t="shared" si="0"/>
-        <v>51</v>
-      </c>
-      <c r="E11" s="5">
-        <v>60</v>
-      </c>
-      <c r="F11" s="5">
-        <v>10000</v>
-      </c>
-      <c r="G11" s="5">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="12" customHeight="1" spans="3:7">
-      <c r="C12" s="2"/>
-      <c r="D12" s="2"/>
-      <c r="E12" s="2"/>
-      <c r="F12" s="2"/>
-      <c r="G12" s="2"/>
-    </row>
-    <row r="13" customHeight="1" spans="3:7">
-      <c r="C13" s="2"/>
-      <c r="D13" s="2"/>
-      <c r="E13" s="2"/>
-      <c r="F13" s="2"/>
-      <c r="G13" s="2"/>
-    </row>
-    <row r="14" customHeight="1" spans="3:7">
-      <c r="C14" s="2"/>
-      <c r="D14" s="2"/>
-      <c r="E14" s="2"/>
-      <c r="F14" s="2"/>
-      <c r="G14" s="2"/>
-    </row>
-    <row r="15" customHeight="1" spans="3:7">
-      <c r="C15" s="2"/>
-      <c r="D15" s="1"/>
-      <c r="E15" s="1"/>
-      <c r="F15" s="2"/>
-    </row>
-    <row r="16" customHeight="1" spans="3:7">
-      <c r="C16" s="2"/>
+    <row r="16" s="1" customFormat="1" spans="1:12 16382:16384">
+      <c r="E16" s="2"/>
+      <c r="F16" s="2"/>
+      <c r="G16" s="9"/>
+      <c r="H16" s="9"/>
+      <c r="I16" s="2"/>
+      <c r="J16" s="2"/>
+      <c r="K16" s="9"/>
+      <c r="XFB16"/>
+      <c r="XFC16"/>
+      <c r="XFD16" s="4"/>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C4:E4 F4 G4 C5:G5 C2:G3" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C2:D5" errorStyle="warning">
       <formula1>COUNTIF($C:$C,C2)&lt;2</formula1>
     </dataValidation>
   </dataValidations>

--- a/Excel/EquipRefineConfig.xlsx
+++ b/Excel/EquipRefineConfig.xlsx
@@ -168,7 +168,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="24">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -179,20 +179,7 @@
     <font>
       <sz val="9"/>
       <color theme="1"/>
-      <name val="微软雅黑"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="9"/>
-      <color theme="1"/>
-      <name val="微软雅黑"/>
+      <name val="等线"/>
       <charset val="134"/>
     </font>
     <font>
@@ -671,157 +658,152 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1142,50 +1124,51 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:XFD16"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="11.5"/>
   <cols>
     <col min="1" max="2" width="9" style="1"/>
     <col min="3" max="3" width="10.1666666666667" style="1" customWidth="1"/>
     <col min="4" max="4" width="8.75" style="1" customWidth="1"/>
-    <col min="5" max="5" width="22.5833333333333" style="2" customWidth="1"/>
-    <col min="6" max="6" width="22.25" style="2" customWidth="1"/>
+    <col min="5" max="5" width="22.5833333333333" style="3" customWidth="1"/>
+    <col min="6" max="6" width="22.25" style="3" customWidth="1"/>
     <col min="7" max="7" width="19.9166666666667" style="3" customWidth="1"/>
     <col min="8" max="8" width="15.0833333333333" style="3" customWidth="1"/>
-    <col min="9" max="9" width="21.5" style="2" customWidth="1"/>
-    <col min="10" max="10" width="20.6666666666667" style="2" customWidth="1"/>
+    <col min="9" max="9" width="21.5" style="3" customWidth="1"/>
+    <col min="10" max="10" width="20.6666666666667" style="3" customWidth="1"/>
     <col min="11" max="11" width="19.8333333333333" style="3" customWidth="1"/>
     <col min="12" max="12" width="10.5" style="1" customWidth="1"/>
     <col min="13" max="16381" width="9" style="1"/>
+    <col min="16382" max="16383" width="9" style="2"/>
     <col min="16384" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="13" spans="1:12 16382:16384">
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
+    <row r="1" s="1" customFormat="1" spans="1:12 16382:16384">
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
       <c r="G1" s="3"/>
       <c r="H1" s="3"/>
-      <c r="I1" s="2"/>
-      <c r="J1" s="2"/>
+      <c r="I1" s="3"/>
+      <c r="J1" s="3"/>
       <c r="K1" s="3"/>
       <c r="L1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" s="1" customFormat="1" ht="13" spans="1:12 16382:16384">
+    <row r="2" s="1" customFormat="1" spans="1:12 16382:16384">
       <c r="C2" s="5"/>
       <c r="D2" s="5"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
       <c r="G2" s="3"/>
       <c r="H2" s="3"/>
-      <c r="I2" s="2"/>
-      <c r="J2" s="2"/>
+      <c r="I2" s="3"/>
+      <c r="J2" s="3"/>
       <c r="K2" s="3"/>
       <c r="L2" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1" ht="13.5" spans="1:12 16382:16384">
+    <row r="3" s="1" customFormat="1" spans="1:12 16382:16384">
       <c r="C3" s="6" t="s">
         <v>1</v>
       </c>
@@ -1198,10 +1181,10 @@
       <c r="F3" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="G3" s="8" t="s">
+      <c r="G3" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="H3" s="8" t="s">
+      <c r="H3" s="7" t="s">
         <v>6</v>
       </c>
       <c r="I3" s="7" t="s">
@@ -1210,12 +1193,12 @@
       <c r="J3" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="K3" s="8" t="s">
+      <c r="K3" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="L3" s="8"/>
+      <c r="L3" s="7"/>
     </row>
-    <row r="4" s="1" customFormat="1" ht="13.5" spans="1:12 16382:16384">
+    <row r="4" s="1" customFormat="1" spans="1:12 16382:16384">
       <c r="C4" s="6" t="s">
         <v>10</v>
       </c>
@@ -1228,10 +1211,10 @@
       <c r="F4" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="G4" s="8" t="s">
+      <c r="G4" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="8" t="s">
+      <c r="H4" s="7" t="s">
         <v>6</v>
       </c>
       <c r="I4" s="7" t="s">
@@ -1240,12 +1223,12 @@
       <c r="J4" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="K4" s="8" t="s">
+      <c r="K4" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="L4" s="8"/>
+      <c r="L4" s="7"/>
     </row>
-    <row r="5" s="1" customFormat="1" ht="13.5" spans="1:12 16382:16384">
+    <row r="5" s="1" customFormat="1" spans="1:12 16382:16384">
       <c r="C5" s="6" t="s">
         <v>11</v>
       </c>
@@ -1258,10 +1241,10 @@
       <c r="F5" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="G5" s="8" t="s">
+      <c r="G5" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="H5" s="8" t="s">
+      <c r="H5" s="7" t="s">
         <v>11</v>
       </c>
       <c r="I5" s="7" t="s">
@@ -1270,381 +1253,381 @@
       <c r="J5" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="K5" s="8" t="s">
+      <c r="K5" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="L5" s="8"/>
+      <c r="L5" s="7"/>
     </row>
-    <row r="6" customFormat="1" ht="24" customHeight="1" spans="1:12 16382:16384">
+    <row r="6" s="2" customFormat="1" ht="24" customHeight="1" spans="1:12 16382:16384">
       <c r="A6" s="1"/>
       <c r="B6" s="1"/>
-      <c r="C6" t="s">
+      <c r="C6" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="D6" t="s">
+      <c r="D6" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="E6" s="10" t="s">
+      <c r="E6" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="F6" s="10" t="s">
+      <c r="F6" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="G6" s="11" t="s">
+      <c r="G6" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="H6" s="9">
+      <c r="H6" s="4">
         <v>2</v>
       </c>
-      <c r="I6" s="10" t="s">
+      <c r="I6" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="J6" s="11" t="s">
+      <c r="J6" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="K6" s="11" t="s">
+      <c r="K6" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="L6" t="s">
+      <c r="L6" s="4" t="s">
         <v>20</v>
       </c>
       <c r="XFB6" s="4"/>
       <c r="XFC6" s="4"/>
     </row>
-    <row r="7" customFormat="1" ht="24" customHeight="1" spans="1:12 16382:16384">
+    <row r="7" s="2" customFormat="1" ht="24" customHeight="1" spans="1:12 16382:16384">
       <c r="A7" s="1"/>
       <c r="B7" s="1"/>
-      <c r="C7" t="s">
+      <c r="C7" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="D7" t="s">
+      <c r="D7" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="E7" s="10" t="s">
+      <c r="E7" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="F7" s="10" t="s">
+      <c r="F7" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="G7" s="11" t="s">
+      <c r="G7" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="H7" s="9">
+      <c r="H7" s="4">
         <v>2</v>
       </c>
-      <c r="I7" s="10" t="s">
+      <c r="I7" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="J7" s="11" t="s">
+      <c r="J7" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="K7" s="11" t="s">
+      <c r="K7" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="L7" t="s">
+      <c r="L7" s="4" t="s">
         <v>23</v>
       </c>
       <c r="XFB7" s="4"/>
       <c r="XFC7" s="4"/>
     </row>
-    <row r="8" customFormat="1" ht="24" customHeight="1" spans="1:12 16382:16384">
+    <row r="8" s="2" customFormat="1" ht="24" customHeight="1" spans="1:12 16382:16384">
       <c r="A8" s="1"/>
       <c r="B8" s="1"/>
-      <c r="C8" t="s">
+      <c r="C8" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="D8" t="s">
+      <c r="D8" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="E8" s="10" t="s">
+      <c r="E8" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="F8" s="10" t="s">
+      <c r="F8" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="G8" s="11" t="s">
+      <c r="G8" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="H8" s="9">
+      <c r="H8" s="4">
         <v>1</v>
       </c>
-      <c r="I8" s="10" t="s">
+      <c r="I8" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="J8" s="11" t="s">
+      <c r="J8" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="K8" s="11" t="s">
+      <c r="K8" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="L8" t="s">
+      <c r="L8" s="4" t="s">
         <v>27</v>
       </c>
       <c r="XFB8" s="4"/>
       <c r="XFC8" s="4"/>
     </row>
-    <row r="9" customFormat="1" ht="24" customHeight="1" spans="1:12 16382:16384">
+    <row r="9" s="2" customFormat="1" ht="24" customHeight="1" spans="1:12 16382:16384">
       <c r="A9" s="1"/>
       <c r="B9" s="1"/>
-      <c r="C9" t="s">
+      <c r="C9" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="D9" t="s">
+      <c r="D9" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="E9" s="10" t="s">
+      <c r="E9" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="F9" s="10" t="s">
+      <c r="F9" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="G9" s="11" t="s">
+      <c r="G9" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="H9" s="9">
+      <c r="H9" s="4">
         <v>1</v>
       </c>
-      <c r="I9" s="10" t="s">
+      <c r="I9" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="J9" s="11" t="s">
+      <c r="J9" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="K9" s="11" t="s">
+      <c r="K9" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="L9" t="s">
+      <c r="L9" s="4" t="s">
         <v>30</v>
       </c>
       <c r="XFB9" s="4"/>
       <c r="XFC9" s="4"/>
     </row>
-    <row r="10" customFormat="1" ht="24" customHeight="1" spans="1:12 16382:16384">
+    <row r="10" s="2" customFormat="1" ht="24" customHeight="1" spans="1:12 16382:16384">
       <c r="A10" s="1"/>
       <c r="B10" s="1"/>
-      <c r="C10" t="s">
+      <c r="C10" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="D10" t="s">
+      <c r="D10" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="E10" s="10" t="s">
+      <c r="E10" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="F10" s="10" t="s">
+      <c r="F10" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="G10" s="11" t="s">
+      <c r="G10" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="H10" s="9">
+      <c r="H10" s="4">
         <v>1</v>
       </c>
-      <c r="I10" s="10" t="s">
+      <c r="I10" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="J10" s="11" t="s">
+      <c r="J10" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="K10" s="11" t="s">
+      <c r="K10" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="L10" t="s">
+      <c r="L10" s="4" t="s">
         <v>32</v>
       </c>
       <c r="XFB10" s="4"/>
       <c r="XFC10" s="4"/>
     </row>
-    <row r="11" customFormat="1" ht="24" customHeight="1" spans="1:12 16382:16384">
+    <row r="11" s="2" customFormat="1" ht="24" customHeight="1" spans="1:12 16382:16384">
       <c r="A11" s="1"/>
       <c r="B11" s="1"/>
-      <c r="C11" t="s">
+      <c r="C11" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="D11" t="s">
+      <c r="D11" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="E11" s="10" t="s">
+      <c r="E11" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="F11" s="10" t="s">
+      <c r="F11" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="G11" s="11" t="s">
+      <c r="G11" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="H11" s="9">
+      <c r="H11" s="4">
         <v>1</v>
       </c>
-      <c r="I11" s="10" t="s">
+      <c r="I11" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="J11" s="11" t="s">
+      <c r="J11" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="K11" s="11" t="s">
+      <c r="K11" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="L11" t="s">
+      <c r="L11" s="4" t="s">
         <v>32</v>
       </c>
       <c r="XFB11" s="4"/>
       <c r="XFC11" s="4"/>
     </row>
-    <row r="12" customFormat="1" ht="24" customHeight="1" spans="1:12 16382:16384">
+    <row r="12" s="2" customFormat="1" ht="24" customHeight="1" spans="1:12 16382:16384">
       <c r="A12" s="1"/>
       <c r="B12" s="1"/>
-      <c r="C12" t="s">
+      <c r="C12" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="D12" t="s">
+      <c r="D12" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="E12" s="10" t="s">
+      <c r="E12" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="F12" s="10" t="s">
+      <c r="F12" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="G12" s="11" t="s">
+      <c r="G12" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="H12" s="9">
+      <c r="H12" s="4">
         <v>1</v>
       </c>
-      <c r="I12" s="10" t="s">
+      <c r="I12" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="J12" s="11" t="s">
+      <c r="J12" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="K12" s="11" t="s">
+      <c r="K12" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="L12" t="s">
+      <c r="L12" s="4" t="s">
         <v>36</v>
       </c>
       <c r="XFB12" s="4"/>
       <c r="XFC12" s="4"/>
     </row>
-    <row r="13" customFormat="1" ht="24" customHeight="1" spans="1:12 16382:16384">
+    <row r="13" s="2" customFormat="1" ht="24" customHeight="1" spans="1:12 16382:16384">
       <c r="A13" s="1"/>
       <c r="B13" s="1"/>
-      <c r="C13" t="s">
+      <c r="C13" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="D13" t="s">
+      <c r="D13" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="E13" s="10" t="s">
+      <c r="E13" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="F13" s="10" t="s">
+      <c r="F13" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="G13" s="11" t="s">
+      <c r="G13" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="H13" s="9">
+      <c r="H13" s="4">
         <v>1</v>
       </c>
-      <c r="I13" s="10" t="s">
+      <c r="I13" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="J13" s="11" t="s">
+      <c r="J13" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="K13" s="11" t="s">
+      <c r="K13" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="L13" t="s">
+      <c r="L13" s="4" t="s">
         <v>36</v>
       </c>
       <c r="XFB13" s="4"/>
       <c r="XFC13" s="4"/>
     </row>
-    <row r="14" customFormat="1" ht="24" customHeight="1" spans="1:12 16382:16384">
+    <row r="14" s="2" customFormat="1" ht="24" customHeight="1" spans="1:12 16382:16384">
       <c r="A14" s="1"/>
       <c r="B14" s="1"/>
-      <c r="C14" t="s">
+      <c r="C14" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="D14" t="s">
+      <c r="D14" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="E14" s="10" t="s">
+      <c r="E14" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="F14" s="10" t="s">
+      <c r="F14" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="G14" s="11" t="s">
+      <c r="G14" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="H14" s="9">
+      <c r="H14" s="4">
         <v>1</v>
       </c>
-      <c r="I14" s="10" t="s">
+      <c r="I14" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="J14" s="11" t="s">
+      <c r="J14" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="K14" s="11" t="s">
+      <c r="K14" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="L14" t="s">
+      <c r="L14" s="4" t="s">
         <v>39</v>
       </c>
       <c r="XFB14" s="4"/>
       <c r="XFC14" s="4"/>
     </row>
-    <row r="15" customFormat="1" ht="24" customHeight="1" spans="1:12 16382:16384">
+    <row r="15" s="2" customFormat="1" ht="24" customHeight="1" spans="1:12 16382:16384">
       <c r="A15" s="1"/>
       <c r="B15" s="1"/>
-      <c r="C15" t="s">
+      <c r="C15" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="D15" t="s">
+      <c r="D15" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="E15" s="10" t="s">
+      <c r="E15" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="F15" s="10" t="s">
+      <c r="F15" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="G15" s="11" t="s">
+      <c r="G15" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="H15" s="9">
+      <c r="H15" s="4">
         <v>1</v>
       </c>
-      <c r="I15" s="10" t="s">
+      <c r="I15" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="J15" s="11" t="s">
+      <c r="J15" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="K15" s="11" t="s">
+      <c r="K15" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="L15" t="s">
+      <c r="L15" s="4" t="s">
         <v>42</v>
       </c>
       <c r="XFB15" s="4"/>
       <c r="XFC15" s="4"/>
     </row>
     <row r="16" s="1" customFormat="1" spans="1:12 16382:16384">
-      <c r="E16" s="2"/>
-      <c r="F16" s="2"/>
-      <c r="G16" s="9"/>
-      <c r="H16" s="9"/>
-      <c r="I16" s="2"/>
-      <c r="J16" s="2"/>
-      <c r="K16" s="9"/>
-      <c r="XFB16"/>
-      <c r="XFC16"/>
+      <c r="E16" s="3"/>
+      <c r="F16" s="3"/>
+      <c r="G16" s="4"/>
+      <c r="H16" s="4"/>
+      <c r="I16" s="3"/>
+      <c r="J16" s="3"/>
+      <c r="K16" s="4"/>
+      <c r="XFB16" s="2"/>
+      <c r="XFC16" s="2"/>
       <c r="XFD16" s="4"/>
     </row>
   </sheetData>

--- a/Excel/EquipRefineConfig.xlsx
+++ b/Excel/EquipRefineConfig.xlsx
@@ -77,7 +77,7 @@
     <t>20001,20002,20003</t>
   </si>
   <si>
-    <t>1,1,1</t>
+    <t>4,4,4</t>
   </si>
   <si>
     <t>0,20,40,60</t>
@@ -788,12 +788,11 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1138,8 +1137,7 @@
     <col min="11" max="11" width="19.8333333333333" style="3" customWidth="1"/>
     <col min="12" max="12" width="10.5" style="1" customWidth="1"/>
     <col min="13" max="16381" width="9" style="1"/>
-    <col min="16382" max="16383" width="9" style="2"/>
-    <col min="16384" max="16384" width="9" style="4"/>
+    <col min="16382" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" spans="1:12 16382:16384">
@@ -1155,8 +1153,8 @@
       </c>
     </row>
     <row r="2" s="1" customFormat="1" spans="1:12 16382:16384">
-      <c r="C2" s="5"/>
-      <c r="D2" s="5"/>
+      <c r="C2" s="4"/>
+      <c r="D2" s="4"/>
       <c r="E2" s="3"/>
       <c r="F2" s="3"/>
       <c r="G2" s="3"/>
@@ -1169,466 +1167,446 @@
       </c>
     </row>
     <row r="3" s="1" customFormat="1" spans="1:12 16382:16384">
-      <c r="C3" s="6" t="s">
+      <c r="C3" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="D3" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="E3" s="7" t="s">
+      <c r="E3" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="F3" s="7" t="s">
+      <c r="F3" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="G3" s="7" t="s">
+      <c r="G3" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="H3" s="7" t="s">
+      <c r="H3" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="I3" s="7" t="s">
+      <c r="I3" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="J3" s="7" t="s">
+      <c r="J3" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="K3" s="7" t="s">
+      <c r="K3" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="L3" s="7"/>
+      <c r="L3" s="6"/>
     </row>
     <row r="4" s="1" customFormat="1" spans="1:12 16382:16384">
-      <c r="C4" s="6" t="s">
+      <c r="C4" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="D4" s="6" t="s">
+      <c r="D4" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="E4" s="7" t="s">
+      <c r="E4" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="F4" s="7" t="s">
+      <c r="F4" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="G4" s="7" t="s">
+      <c r="G4" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="7" t="s">
+      <c r="H4" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="I4" s="7" t="s">
+      <c r="I4" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="J4" s="7" t="s">
+      <c r="J4" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="K4" s="7" t="s">
+      <c r="K4" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="L4" s="7"/>
+      <c r="L4" s="6"/>
     </row>
     <row r="5" s="1" customFormat="1" spans="1:12 16382:16384">
-      <c r="C5" s="6" t="s">
+      <c r="C5" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="D5" s="6" t="s">
+      <c r="D5" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="E5" s="7" t="s">
+      <c r="E5" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="F5" s="7" t="s">
+      <c r="F5" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="G5" s="7" t="s">
+      <c r="G5" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="H5" s="7" t="s">
+      <c r="H5" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="I5" s="7" t="s">
+      <c r="I5" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="J5" s="7" t="s">
+      <c r="J5" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="K5" s="7" t="s">
+      <c r="K5" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="L5" s="7"/>
+      <c r="L5" s="6"/>
     </row>
     <row r="6" s="2" customFormat="1" ht="24" customHeight="1" spans="1:12 16382:16384">
       <c r="A6" s="1"/>
       <c r="B6" s="1"/>
-      <c r="C6" s="4" t="s">
+      <c r="C6" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="D6" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="E6" s="8" t="s">
+      <c r="E6" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="F6" s="8" t="s">
+      <c r="F6" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="G6" s="8" t="s">
+      <c r="G6" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="H6" s="4">
+      <c r="H6" s="2">
         <v>2</v>
       </c>
-      <c r="I6" s="8" t="s">
+      <c r="I6" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="J6" s="8" t="s">
+      <c r="J6" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="K6" s="8" t="s">
+      <c r="K6" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="L6" s="4" t="s">
+      <c r="L6" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="XFB6" s="4"/>
-      <c r="XFC6" s="4"/>
     </row>
     <row r="7" s="2" customFormat="1" ht="24" customHeight="1" spans="1:12 16382:16384">
       <c r="A7" s="1"/>
       <c r="B7" s="1"/>
-      <c r="C7" s="4" t="s">
+      <c r="C7" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="D7" s="4" t="s">
+      <c r="D7" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="E7" s="8" t="s">
+      <c r="E7" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="F7" s="8" t="s">
+      <c r="F7" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="G7" s="8" t="s">
+      <c r="G7" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="H7" s="4">
+      <c r="H7" s="2">
         <v>2</v>
       </c>
-      <c r="I7" s="8" t="s">
+      <c r="I7" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="J7" s="8" t="s">
+      <c r="J7" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="K7" s="8" t="s">
+      <c r="K7" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="L7" s="4" t="s">
+      <c r="L7" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="XFB7" s="4"/>
-      <c r="XFC7" s="4"/>
     </row>
     <row r="8" s="2" customFormat="1" ht="24" customHeight="1" spans="1:12 16382:16384">
       <c r="A8" s="1"/>
       <c r="B8" s="1"/>
-      <c r="C8" s="4" t="s">
+      <c r="C8" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="D8" s="4" t="s">
+      <c r="D8" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="E8" s="8" t="s">
+      <c r="E8" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="F8" s="8" t="s">
+      <c r="F8" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="G8" s="8" t="s">
+      <c r="G8" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="H8" s="4">
+      <c r="H8" s="2">
         <v>1</v>
       </c>
-      <c r="I8" s="8" t="s">
+      <c r="I8" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="J8" s="8" t="s">
+      <c r="J8" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="K8" s="8" t="s">
+      <c r="K8" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="L8" s="4" t="s">
+      <c r="L8" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="XFB8" s="4"/>
-      <c r="XFC8" s="4"/>
     </row>
     <row r="9" s="2" customFormat="1" ht="24" customHeight="1" spans="1:12 16382:16384">
       <c r="A9" s="1"/>
       <c r="B9" s="1"/>
-      <c r="C9" s="4" t="s">
+      <c r="C9" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="D9" s="4" t="s">
+      <c r="D9" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="E9" s="8" t="s">
+      <c r="E9" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="F9" s="8" t="s">
+      <c r="F9" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="G9" s="8" t="s">
+      <c r="G9" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="H9" s="4">
+      <c r="H9" s="2">
         <v>1</v>
       </c>
-      <c r="I9" s="8" t="s">
+      <c r="I9" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="J9" s="8" t="s">
+      <c r="J9" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="K9" s="8" t="s">
+      <c r="K9" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="L9" s="4" t="s">
+      <c r="L9" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="XFB9" s="4"/>
-      <c r="XFC9" s="4"/>
     </row>
     <row r="10" s="2" customFormat="1" ht="24" customHeight="1" spans="1:12 16382:16384">
       <c r="A10" s="1"/>
       <c r="B10" s="1"/>
-      <c r="C10" s="4" t="s">
+      <c r="C10" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="D10" s="4" t="s">
+      <c r="D10" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="E10" s="8" t="s">
+      <c r="E10" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="F10" s="8" t="s">
+      <c r="F10" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="G10" s="8" t="s">
+      <c r="G10" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="H10" s="4">
+      <c r="H10" s="2">
         <v>1</v>
       </c>
-      <c r="I10" s="8" t="s">
+      <c r="I10" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="J10" s="8" t="s">
+      <c r="J10" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="K10" s="8" t="s">
+      <c r="K10" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="L10" s="4" t="s">
+      <c r="L10" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="XFB10" s="4"/>
-      <c r="XFC10" s="4"/>
     </row>
     <row r="11" s="2" customFormat="1" ht="24" customHeight="1" spans="1:12 16382:16384">
       <c r="A11" s="1"/>
       <c r="B11" s="1"/>
-      <c r="C11" s="4" t="s">
+      <c r="C11" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="D11" s="4" t="s">
+      <c r="D11" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="E11" s="8" t="s">
+      <c r="E11" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="F11" s="8" t="s">
+      <c r="F11" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="G11" s="8" t="s">
+      <c r="G11" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="H11" s="4">
+      <c r="H11" s="2">
         <v>1</v>
       </c>
-      <c r="I11" s="8" t="s">
+      <c r="I11" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="J11" s="8" t="s">
+      <c r="J11" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="K11" s="8" t="s">
+      <c r="K11" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="L11" s="4" t="s">
+      <c r="L11" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="XFB11" s="4"/>
-      <c r="XFC11" s="4"/>
     </row>
     <row r="12" s="2" customFormat="1" ht="24" customHeight="1" spans="1:12 16382:16384">
       <c r="A12" s="1"/>
       <c r="B12" s="1"/>
-      <c r="C12" s="4" t="s">
+      <c r="C12" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="D12" s="4" t="s">
+      <c r="D12" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="E12" s="8" t="s">
+      <c r="E12" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="F12" s="8" t="s">
+      <c r="F12" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="G12" s="8" t="s">
+      <c r="G12" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="H12" s="4">
+      <c r="H12" s="2">
         <v>1</v>
       </c>
-      <c r="I12" s="8" t="s">
+      <c r="I12" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="J12" s="8" t="s">
+      <c r="J12" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="K12" s="8" t="s">
+      <c r="K12" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="L12" s="4" t="s">
+      <c r="L12" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="XFB12" s="4"/>
-      <c r="XFC12" s="4"/>
     </row>
     <row r="13" s="2" customFormat="1" ht="24" customHeight="1" spans="1:12 16382:16384">
       <c r="A13" s="1"/>
       <c r="B13" s="1"/>
-      <c r="C13" s="4" t="s">
+      <c r="C13" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="D13" s="4" t="s">
+      <c r="D13" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="E13" s="8" t="s">
+      <c r="E13" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="F13" s="8" t="s">
+      <c r="F13" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="G13" s="8" t="s">
+      <c r="G13" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="H13" s="4">
+      <c r="H13" s="2">
         <v>1</v>
       </c>
-      <c r="I13" s="8" t="s">
+      <c r="I13" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="J13" s="8" t="s">
+      <c r="J13" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="K13" s="8" t="s">
+      <c r="K13" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="L13" s="4" t="s">
+      <c r="L13" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="XFB13" s="4"/>
-      <c r="XFC13" s="4"/>
     </row>
     <row r="14" s="2" customFormat="1" ht="24" customHeight="1" spans="1:12 16382:16384">
       <c r="A14" s="1"/>
       <c r="B14" s="1"/>
-      <c r="C14" s="4" t="s">
+      <c r="C14" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="D14" s="4" t="s">
+      <c r="D14" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="E14" s="8" t="s">
+      <c r="E14" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="F14" s="8" t="s">
+      <c r="F14" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="G14" s="8" t="s">
+      <c r="G14" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="H14" s="4">
+      <c r="H14" s="2">
         <v>1</v>
       </c>
-      <c r="I14" s="8" t="s">
+      <c r="I14" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="J14" s="8" t="s">
+      <c r="J14" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="K14" s="8" t="s">
+      <c r="K14" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="L14" s="4" t="s">
+      <c r="L14" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="XFB14" s="4"/>
-      <c r="XFC14" s="4"/>
     </row>
     <row r="15" s="2" customFormat="1" ht="24" customHeight="1" spans="1:12 16382:16384">
       <c r="A15" s="1"/>
       <c r="B15" s="1"/>
-      <c r="C15" s="4" t="s">
+      <c r="C15" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="D15" s="4" t="s">
+      <c r="D15" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="E15" s="8" t="s">
+      <c r="E15" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="F15" s="8" t="s">
+      <c r="F15" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="G15" s="8" t="s">
+      <c r="G15" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="H15" s="4">
+      <c r="H15" s="2">
         <v>1</v>
       </c>
-      <c r="I15" s="8" t="s">
+      <c r="I15" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="J15" s="8" t="s">
+      <c r="J15" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="K15" s="8" t="s">
+      <c r="K15" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="L15" s="4" t="s">
+      <c r="L15" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="XFB15" s="4"/>
-      <c r="XFC15" s="4"/>
     </row>
     <row r="16" s="1" customFormat="1" spans="1:12 16382:16384">
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
-      <c r="G16" s="4"/>
-      <c r="H16" s="4"/>
+      <c r="G16" s="2"/>
+      <c r="H16" s="2"/>
       <c r="I16" s="3"/>
       <c r="J16" s="3"/>
-      <c r="K16" s="4"/>
+      <c r="K16" s="2"/>
       <c r="XFB16" s="2"/>
       <c r="XFC16" s="2"/>
-      <c r="XFD16" s="4"/>
+      <c r="XFD16" s="2"/>
     </row>
   </sheetData>
   <dataValidations count="1">

--- a/Excel/EquipRefineConfig.xlsx
+++ b/Excel/EquipRefineConfig.xlsx
@@ -83,54 +83,57 @@
     <t>0,20,40,60</t>
   </si>
   <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>30</t>
+  </si>
+  <si>
+    <t>攻速</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>诅咒</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>冷却</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>闪避</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>命中</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
     <t>7</t>
   </si>
   <si>
-    <t>30</t>
-  </si>
-  <si>
-    <t>幸运</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>诅咒</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>13</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>命中</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>14</t>
-  </si>
-  <si>
-    <t>闪避</t>
-  </si>
-  <si>
-    <t>11</t>
-  </si>
-  <si>
-    <t>攻速</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
     <t>22</t>
   </si>
   <si>
@@ -147,9 +150,6 @@
   </si>
   <si>
     <t>抗暴率</t>
-  </si>
-  <si>
-    <t>10</t>
   </si>
   <si>
     <t>12</t>
@@ -1123,7 +1123,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:XFD16"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="11.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="2" width="9" style="1"/>
     <col min="3" max="3" width="10.1666666666667" style="1" customWidth="1"/>
@@ -1140,7 +1140,7 @@
     <col min="16382" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:12 16382:16384">
+    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:12 16382:16384">
       <c r="E1" s="3"/>
       <c r="F1" s="3"/>
       <c r="G1" s="3"/>
@@ -1152,7 +1152,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" s="1" customFormat="1" spans="1:12 16382:16384">
+    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:12 16382:16384">
       <c r="C2" s="4"/>
       <c r="D2" s="4"/>
       <c r="E2" s="3"/>
@@ -1166,7 +1166,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1" spans="1:12 16382:16384">
+    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:12 16382:16384">
       <c r="C3" s="5" t="s">
         <v>1</v>
       </c>
@@ -1196,7 +1196,7 @@
       </c>
       <c r="L3" s="6"/>
     </row>
-    <row r="4" s="1" customFormat="1" spans="1:12 16382:16384">
+    <row r="4" s="1" customFormat="1" customHeight="1" spans="1:12 16382:16384">
       <c r="C4" s="5" t="s">
         <v>10</v>
       </c>
@@ -1226,7 +1226,7 @@
       </c>
       <c r="L4" s="6"/>
     </row>
-    <row r="5" s="1" customFormat="1" spans="1:12 16382:16384">
+    <row r="5" s="1" customFormat="1" customHeight="1" spans="1:12 16382:16384">
       <c r="C5" s="5" t="s">
         <v>11</v>
       </c>
@@ -1256,7 +1256,7 @@
       </c>
       <c r="L5" s="6"/>
     </row>
-    <row r="6" s="2" customFormat="1" ht="24" customHeight="1" spans="1:12 16382:16384">
+    <row r="6" s="2" customFormat="1" customHeight="1" spans="1:12 16382:16384">
       <c r="A6" s="1"/>
       <c r="B6" s="1"/>
       <c r="C6" s="2" t="s">
@@ -1281,23 +1281,23 @@
         <v>18</v>
       </c>
       <c r="J6" s="7" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="K6" s="7" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
-    <row r="7" s="2" customFormat="1" ht="24" customHeight="1" spans="1:12 16382:16384">
+    <row r="7" s="2" customFormat="1" customHeight="1" spans="1:12 16382:16384">
       <c r="A7" s="1"/>
       <c r="B7" s="1"/>
       <c r="C7" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E7" s="7" t="s">
         <v>15</v>
@@ -1312,26 +1312,26 @@
         <v>2</v>
       </c>
       <c r="I7" s="7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J7" s="7" t="s">
         <v>14</v>
       </c>
       <c r="K7" s="7" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L7" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
-    <row r="8" s="2" customFormat="1" ht="24" customHeight="1" spans="1:12 16382:16384">
+    <row r="8" s="2" customFormat="1" customHeight="1" spans="1:12 16382:16384">
       <c r="A8" s="1"/>
       <c r="B8" s="1"/>
       <c r="C8" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E8" s="7" t="s">
         <v>15</v>
@@ -1346,26 +1346,26 @@
         <v>1</v>
       </c>
       <c r="I8" s="7" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="J8" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="K8" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="L8" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K8" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="L8" s="2" t="s">
-        <v>27</v>
-      </c>
     </row>
-    <row r="9" s="2" customFormat="1" ht="24" customHeight="1" spans="1:12 16382:16384">
+    <row r="9" s="2" customFormat="1" customHeight="1" spans="1:12 16382:16384">
       <c r="A9" s="1"/>
       <c r="B9" s="1"/>
       <c r="C9" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E9" s="7" t="s">
         <v>15</v>
@@ -1380,26 +1380,26 @@
         <v>1</v>
       </c>
       <c r="I9" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="J9" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="J9" s="7" t="s">
-        <v>26</v>
-      </c>
       <c r="K9" s="7" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L9" s="2" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="10" s="2" customFormat="1" ht="24" customHeight="1" spans="1:12 16382:16384">
+    <row r="10" s="2" customFormat="1" customHeight="1" spans="1:12 16382:16384">
       <c r="A10" s="1"/>
       <c r="B10" s="1"/>
       <c r="C10" s="2" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="E10" s="7" t="s">
         <v>15</v>
@@ -1417,16 +1417,16 @@
         <v>31</v>
       </c>
       <c r="J10" s="7" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="K10" s="7" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L10" s="2" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="11" s="2" customFormat="1" ht="24" customHeight="1" spans="1:12 16382:16384">
+    <row r="11" s="2" customFormat="1" customHeight="1" spans="1:12 16382:16384">
       <c r="A11" s="1"/>
       <c r="B11" s="1"/>
       <c r="C11" s="2" t="s">
@@ -1448,26 +1448,26 @@
         <v>1</v>
       </c>
       <c r="I11" s="7" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="J11" s="7" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="K11" s="7" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L11" s="2" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="12" s="2" customFormat="1" ht="24" customHeight="1" spans="1:12 16382:16384">
+    <row r="12" s="2" customFormat="1" customHeight="1" spans="1:12 16382:16384">
       <c r="A12" s="1"/>
       <c r="B12" s="1"/>
       <c r="C12" s="2" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="E12" s="7" t="s">
         <v>15</v>
@@ -1482,26 +1482,26 @@
         <v>1</v>
       </c>
       <c r="I12" s="7" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J12" s="7" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K12" s="7" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L12" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
-    <row r="13" s="2" customFormat="1" ht="24" customHeight="1" spans="1:12 16382:16384">
+    <row r="13" s="2" customFormat="1" customHeight="1" spans="1:12 16382:16384">
       <c r="A13" s="1"/>
       <c r="B13" s="1"/>
       <c r="C13" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E13" s="7" t="s">
         <v>15</v>
@@ -1516,26 +1516,26 @@
         <v>1</v>
       </c>
       <c r="I13" s="7" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J13" s="7" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K13" s="7" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L13" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
-    <row r="14" s="2" customFormat="1" ht="24" customHeight="1" spans="1:12 16382:16384">
+    <row r="14" s="2" customFormat="1" customHeight="1" spans="1:12 16382:16384">
       <c r="A14" s="1"/>
       <c r="B14" s="1"/>
       <c r="C14" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E14" s="7" t="s">
         <v>15</v>
@@ -1550,26 +1550,26 @@
         <v>1</v>
       </c>
       <c r="I14" s="7" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="J14" s="7" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="K14" s="7" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L14" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
-    <row r="15" s="2" customFormat="1" ht="24" customHeight="1" spans="1:12 16382:16384">
+    <row r="15" s="2" customFormat="1" customHeight="1" spans="1:12 16382:16384">
       <c r="A15" s="1"/>
       <c r="B15" s="1"/>
       <c r="C15" s="2" t="s">
-        <v>40</v>
+        <v>19</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>40</v>
+        <v>19</v>
       </c>
       <c r="E15" s="7" t="s">
         <v>15</v>
@@ -1587,16 +1587,16 @@
         <v>41</v>
       </c>
       <c r="J15" s="7" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="K15" s="7" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L15" s="2" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="16" s="1" customFormat="1" spans="1:12 16382:16384">
+    <row r="16" s="1" customFormat="1" customHeight="1" spans="1:12 16382:16384">
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
       <c r="G16" s="2"/>

--- a/Excel/EquipRefineConfig.xlsx
+++ b/Excel/EquipRefineConfig.xlsx
@@ -77,10 +77,10 @@
     <t>20001,20002,20003</t>
   </si>
   <si>
-    <t>4,4,4</t>
-  </si>
-  <si>
-    <t>0,20,40,60</t>
+    <t>4,2,4</t>
+  </si>
+  <si>
+    <t>0,30,60,90</t>
   </si>
   <si>
     <t>11</t>

--- a/Excel/EquipRefineConfig.xlsx
+++ b/Excel/EquipRefineConfig.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="42">
   <si>
     <t>#</t>
   </si>
@@ -47,9 +47,6 @@
     <t>RequireLevel</t>
   </si>
   <si>
-    <t>FeeBase</t>
-  </si>
-  <si>
     <t>SpeAtrList</t>
   </si>
   <si>
@@ -74,13 +71,13 @@
     <t>1</t>
   </si>
   <si>
-    <t>20001,20002,20003</t>
-  </si>
-  <si>
-    <t>4,2,4</t>
-  </si>
-  <si>
-    <t>0,30,60,90</t>
+    <t>20001,20003</t>
+  </si>
+  <si>
+    <t>4,4</t>
+  </si>
+  <si>
+    <t>0,30</t>
   </si>
   <si>
     <t>11</t>
@@ -1122,7 +1119,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:XFD16"/>
+  <dimension ref="A1:XFC16"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="2" width="9" style="1"/>
@@ -1131,28 +1128,26 @@
     <col min="5" max="5" width="22.5833333333333" style="3" customWidth="1"/>
     <col min="6" max="6" width="22.25" style="3" customWidth="1"/>
     <col min="7" max="7" width="19.9166666666667" style="3" customWidth="1"/>
-    <col min="8" max="8" width="15.0833333333333" style="3" customWidth="1"/>
-    <col min="9" max="9" width="21.5" style="3" customWidth="1"/>
-    <col min="10" max="10" width="20.6666666666667" style="3" customWidth="1"/>
-    <col min="11" max="11" width="19.8333333333333" style="3" customWidth="1"/>
-    <col min="12" max="12" width="10.5" style="1" customWidth="1"/>
-    <col min="13" max="16381" width="9" style="1"/>
-    <col min="16382" max="16384" width="9" style="2"/>
+    <col min="8" max="8" width="21.5" style="3" customWidth="1"/>
+    <col min="9" max="9" width="20.6666666666667" style="3" customWidth="1"/>
+    <col min="10" max="10" width="19.8333333333333" style="3" customWidth="1"/>
+    <col min="11" max="11" width="10.5" style="1" customWidth="1"/>
+    <col min="12" max="16380" width="9" style="1"/>
+    <col min="16381" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:12 16382:16384">
+    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:11 16381:16383">
       <c r="E1" s="3"/>
       <c r="F1" s="3"/>
       <c r="G1" s="3"/>
       <c r="H1" s="3"/>
       <c r="I1" s="3"/>
       <c r="J1" s="3"/>
-      <c r="K1" s="3"/>
-      <c r="L1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:12 16382:16384">
+    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:11 16381:16383">
       <c r="C2" s="4"/>
       <c r="D2" s="4"/>
       <c r="E2" s="3"/>
@@ -1161,12 +1156,11 @@
       <c r="H2" s="3"/>
       <c r="I2" s="3"/>
       <c r="J2" s="3"/>
-      <c r="K2" s="3"/>
-      <c r="L2" s="1" t="s">
+      <c r="K2" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:12 16382:16384">
+    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:11 16381:16383">
       <c r="C3" s="5" t="s">
         <v>1</v>
       </c>
@@ -1191,14 +1185,11 @@
       <c r="J3" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="K3" s="6" t="s">
+      <c r="K3" s="6"/>
+    </row>
+    <row r="4" s="1" customFormat="1" customHeight="1" spans="1:11 16381:16383">
+      <c r="C4" s="5" t="s">
         <v>9</v>
-      </c>
-      <c r="L3" s="6"/>
-    </row>
-    <row r="4" s="1" customFormat="1" customHeight="1" spans="1:12 16382:16384">
-      <c r="C4" s="5" t="s">
-        <v>10</v>
       </c>
       <c r="D4" s="5" t="s">
         <v>2</v>
@@ -1221,26 +1212,23 @@
       <c r="J4" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="K4" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="L4" s="6"/>
+      <c r="K4" s="6"/>
     </row>
-    <row r="5" s="1" customFormat="1" customHeight="1" spans="1:12 16382:16384">
+    <row r="5" s="1" customFormat="1" customHeight="1" spans="1:11 16381:16383">
       <c r="C5" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="E5" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="F5" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="G5" s="6" t="s">
         <v>11</v>
-      </c>
-      <c r="E5" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="F5" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="G5" s="6" t="s">
-        <v>12</v>
       </c>
       <c r="H5" s="6" t="s">
         <v>11</v>
@@ -1249,33 +1237,30 @@
         <v>12</v>
       </c>
       <c r="J5" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="K5" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="L5" s="6"/>
+        <v>11</v>
+      </c>
+      <c r="K5" s="6"/>
     </row>
-    <row r="6" s="2" customFormat="1" customHeight="1" spans="1:12 16382:16384">
+    <row r="6" s="2" customFormat="1" customHeight="1" spans="1:11 16381:16383">
       <c r="A6" s="1"/>
       <c r="B6" s="1"/>
       <c r="C6" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E6" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="D6" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E6" s="7" t="s">
+      <c r="F6" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="F6" s="7" t="s">
+      <c r="G6" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="G6" s="7" t="s">
+      <c r="H6" s="7" t="s">
         <v>17</v>
-      </c>
-      <c r="H6" s="2">
-        <v>2</v>
       </c>
       <c r="I6" s="7" t="s">
         <v>18</v>
@@ -1283,330 +1268,299 @@
       <c r="J6" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="K6" s="7" t="s">
+      <c r="K6" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="L6" s="2" t="s">
-        <v>21</v>
-      </c>
     </row>
-    <row r="7" s="2" customFormat="1" customHeight="1" spans="1:12 16382:16384">
+    <row r="7" s="2" customFormat="1" customHeight="1" spans="1:11 16381:16383">
       <c r="A7" s="1"/>
       <c r="B7" s="1"/>
       <c r="C7" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="F7" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="G7" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="H7" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="D7" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="E7" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="F7" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="G7" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="H7" s="2">
-        <v>2</v>
-      </c>
       <c r="I7" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="J7" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="K7" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="J7" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="K7" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="L7" s="2" t="s">
-        <v>24</v>
-      </c>
     </row>
-    <row r="8" s="2" customFormat="1" customHeight="1" spans="1:12 16382:16384">
+    <row r="8" s="2" customFormat="1" customHeight="1" spans="1:11 16381:16383">
       <c r="A8" s="1"/>
       <c r="B8" s="1"/>
       <c r="C8" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E8" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="F8" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="F8" s="7" t="s">
+      <c r="G8" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="G8" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="H8" s="2">
-        <v>1</v>
+      <c r="H8" s="7" t="s">
+        <v>18</v>
       </c>
       <c r="I8" s="7" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J8" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="K8" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="L8" s="2" t="s">
-        <v>26</v>
+      <c r="K8" s="2" t="s">
+        <v>25</v>
       </c>
     </row>
-    <row r="9" s="2" customFormat="1" customHeight="1" spans="1:12 16382:16384">
+    <row r="9" s="2" customFormat="1" customHeight="1" spans="1:11 16381:16383">
       <c r="A9" s="1"/>
       <c r="B9" s="1"/>
       <c r="C9" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="F9" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="G9" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="H9" s="7" t="s">
         <v>27</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="E9" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="F9" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="G9" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="H9" s="2">
-        <v>1</v>
       </c>
       <c r="I9" s="7" t="s">
         <v>28</v>
       </c>
       <c r="J9" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="K9" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="K9" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="L9" s="2" t="s">
-        <v>30</v>
-      </c>
     </row>
-    <row r="10" s="2" customFormat="1" customHeight="1" spans="1:12 16382:16384">
+    <row r="10" s="2" customFormat="1" customHeight="1" spans="1:11 16381:16383">
       <c r="A10" s="1"/>
       <c r="B10" s="1"/>
       <c r="C10" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E10" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="F10" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="F10" s="7" t="s">
+      <c r="G10" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="G10" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="H10" s="2">
-        <v>1</v>
+      <c r="H10" s="7" t="s">
+        <v>30</v>
       </c>
       <c r="I10" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="J10" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="K10" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="J10" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="K10" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="L10" s="2" t="s">
-        <v>32</v>
-      </c>
     </row>
-    <row r="11" s="2" customFormat="1" customHeight="1" spans="1:12 16382:16384">
+    <row r="11" s="2" customFormat="1" customHeight="1" spans="1:11 16381:16383">
       <c r="A11" s="1"/>
       <c r="B11" s="1"/>
       <c r="C11" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E11" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="F11" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="F11" s="7" t="s">
+      <c r="G11" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="G11" s="7" t="s">
+      <c r="H11" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="H11" s="2">
-        <v>1</v>
-      </c>
       <c r="I11" s="7" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="J11" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="K11" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="L11" s="2" t="s">
-        <v>32</v>
+        <v>19</v>
+      </c>
+      <c r="K11" s="2" t="s">
+        <v>31</v>
       </c>
     </row>
-    <row r="12" s="2" customFormat="1" customHeight="1" spans="1:12 16382:16384">
+    <row r="12" s="2" customFormat="1" customHeight="1" spans="1:11 16381:16383">
       <c r="A12" s="1"/>
       <c r="B12" s="1"/>
       <c r="C12" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="E12" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="F12" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="G12" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="H12" s="7" t="s">
         <v>34</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="E12" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="F12" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="G12" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="H12" s="2">
-        <v>1</v>
       </c>
       <c r="I12" s="7" t="s">
         <v>35</v>
       </c>
       <c r="J12" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="K12" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="K12" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="L12" s="2" t="s">
-        <v>37</v>
-      </c>
     </row>
-    <row r="13" s="2" customFormat="1" customHeight="1" spans="1:12 16382:16384">
+    <row r="13" s="2" customFormat="1" customHeight="1" spans="1:11 16381:16383">
       <c r="A13" s="1"/>
       <c r="B13" s="1"/>
       <c r="C13" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E13" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="F13" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="F13" s="7" t="s">
+      <c r="G13" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="G13" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="H13" s="2">
-        <v>1</v>
+      <c r="H13" s="7" t="s">
+        <v>34</v>
       </c>
       <c r="I13" s="7" t="s">
         <v>35</v>
       </c>
       <c r="J13" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="K13" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="K13" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="L13" s="2" t="s">
-        <v>37</v>
-      </c>
     </row>
-    <row r="14" s="2" customFormat="1" customHeight="1" spans="1:12 16382:16384">
+    <row r="14" s="2" customFormat="1" customHeight="1" spans="1:11 16381:16383">
       <c r="A14" s="1"/>
       <c r="B14" s="1"/>
       <c r="C14" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="E14" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="F14" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="G14" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="H14" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="D14" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="E14" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="F14" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="G14" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="H14" s="2">
-        <v>1</v>
-      </c>
       <c r="I14" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="J14" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="K14" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="J14" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="K14" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="L14" s="2" t="s">
-        <v>40</v>
-      </c>
     </row>
-    <row r="15" s="2" customFormat="1" customHeight="1" spans="1:12 16382:16384">
+    <row r="15" s="2" customFormat="1" customHeight="1" spans="1:11 16381:16383">
       <c r="A15" s="1"/>
       <c r="B15" s="1"/>
       <c r="C15" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E15" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="F15" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="G15" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="H15" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="I15" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="J15" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="D15" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="E15" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="F15" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="G15" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="H15" s="2">
-        <v>1</v>
-      </c>
-      <c r="I15" s="7" t="s">
+      <c r="K15" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="J15" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="K15" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="L15" s="2" t="s">
-        <v>42</v>
-      </c>
     </row>
-    <row r="16" s="1" customFormat="1" customHeight="1" spans="1:12 16382:16384">
+    <row r="16" s="1" customFormat="1" customHeight="1" spans="1:11 16381:16383">
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
       <c r="G16" s="2"/>
-      <c r="H16" s="2"/>
+      <c r="H16" s="3"/>
       <c r="I16" s="3"/>
-      <c r="J16" s="3"/>
-      <c r="K16" s="2"/>
+      <c r="J16" s="2"/>
+      <c r="XFA16" s="2"/>
       <c r="XFB16" s="2"/>
       <c r="XFC16" s="2"/>
-      <c r="XFD16" s="2"/>
     </row>
   </sheetData>
   <dataValidations count="1">

--- a/Excel/EquipRefineConfig.xlsx
+++ b/Excel/EquipRefineConfig.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="41">
   <si>
     <t>#</t>
   </si>
@@ -71,13 +71,13 @@
     <t>1</t>
   </si>
   <si>
-    <t>20001,20003</t>
-  </si>
-  <si>
-    <t>4,4</t>
-  </si>
-  <si>
-    <t>0,30</t>
+    <t>20001,20002,20003</t>
+  </si>
+  <si>
+    <t>4,4,2</t>
+  </si>
+  <si>
+    <t>0,30,60</t>
   </si>
   <si>
     <t>11</t>
@@ -122,19 +122,16 @@
     <t>13</t>
   </si>
   <si>
+    <t>20</t>
+  </si>
+  <si>
     <t>命中</t>
   </si>
   <si>
-    <t>6</t>
-  </si>
-  <si>
     <t>7</t>
   </si>
   <si>
     <t>22</t>
-  </si>
-  <si>
-    <t>20</t>
   </si>
   <si>
     <t>爆伤</t>
@@ -1119,15 +1116,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:XFC16"/>
+  <dimension ref="A1:XFC14"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="2" width="9" style="1"/>
     <col min="3" max="3" width="10.1666666666667" style="1" customWidth="1"/>
     <col min="4" max="4" width="8.75" style="1" customWidth="1"/>
-    <col min="5" max="5" width="22.5833333333333" style="3" customWidth="1"/>
-    <col min="6" max="6" width="22.25" style="3" customWidth="1"/>
-    <col min="7" max="7" width="19.9166666666667" style="3" customWidth="1"/>
+    <col min="5" max="5" width="20.6666666666667" style="3" customWidth="1"/>
+    <col min="6" max="6" width="16.75" style="3" customWidth="1"/>
+    <col min="7" max="7" width="18.0833333333333" style="3" customWidth="1"/>
     <col min="8" max="8" width="21.5" style="3" customWidth="1"/>
     <col min="9" max="9" width="20.6666666666667" style="3" customWidth="1"/>
     <col min="10" max="10" width="19.8333333333333" style="3" customWidth="1"/>
@@ -1387,23 +1384,23 @@
         <v>30</v>
       </c>
       <c r="I10" s="7" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="J10" s="7" t="s">
         <v>19</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="11" s="2" customFormat="1" customHeight="1" spans="1:11 16381:16383">
       <c r="A11" s="1"/>
       <c r="B11" s="1"/>
       <c r="C11" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E11" s="7" t="s">
         <v>14</v>
@@ -1415,26 +1412,26 @@
         <v>16</v>
       </c>
       <c r="H11" s="7" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="I11" s="7" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="J11" s="7" t="s">
         <v>19</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
     </row>
     <row r="12" s="2" customFormat="1" customHeight="1" spans="1:11 16381:16383">
       <c r="A12" s="1"/>
       <c r="B12" s="1"/>
       <c r="C12" s="2" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E12" s="7" t="s">
         <v>14</v>
@@ -1446,26 +1443,26 @@
         <v>16</v>
       </c>
       <c r="H12" s="7" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="I12" s="7" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="J12" s="7" t="s">
         <v>19</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="13" s="2" customFormat="1" customHeight="1" spans="1:11 16381:16383">
       <c r="A13" s="1"/>
       <c r="B13" s="1"/>
       <c r="C13" s="2" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="E13" s="7" t="s">
         <v>14</v>
@@ -1477,90 +1474,28 @@
         <v>16</v>
       </c>
       <c r="H13" s="7" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="I13" s="7" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="J13" s="7" t="s">
         <v>19</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
     </row>
-    <row r="14" s="2" customFormat="1" customHeight="1" spans="1:11 16381:16383">
-      <c r="A14" s="1"/>
-      <c r="B14" s="1"/>
-      <c r="C14" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="E14" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="F14" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="G14" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="H14" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="I14" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="J14" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="K14" s="2" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="15" s="2" customFormat="1" customHeight="1" spans="1:11 16381:16383">
-      <c r="A15" s="1"/>
-      <c r="B15" s="1"/>
-      <c r="C15" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E15" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="F15" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="G15" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="H15" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="I15" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="J15" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="K15" s="2" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="16" s="1" customFormat="1" customHeight="1" spans="1:11 16381:16383">
-      <c r="E16" s="3"/>
-      <c r="F16" s="3"/>
-      <c r="G16" s="2"/>
-      <c r="H16" s="3"/>
-      <c r="I16" s="3"/>
-      <c r="J16" s="2"/>
-      <c r="XFA16" s="2"/>
-      <c r="XFB16" s="2"/>
-      <c r="XFC16" s="2"/>
+    <row r="14" s="1" customFormat="1" customHeight="1" spans="1:11 16381:16383">
+      <c r="E14" s="3"/>
+      <c r="F14" s="3"/>
+      <c r="G14" s="2"/>
+      <c r="H14" s="3"/>
+      <c r="I14" s="3"/>
+      <c r="J14" s="2"/>
+      <c r="XFA14" s="2"/>
+      <c r="XFB14" s="2"/>
+      <c r="XFC14" s="2"/>
     </row>
   </sheetData>
   <dataValidations count="1">

--- a/Excel/EquipRefineConfig.xlsx
+++ b/Excel/EquipRefineConfig.xlsx
@@ -95,10 +95,13 @@
     <t>2</t>
   </si>
   <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>诅咒</t>
+    <t>25</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>抗暴率</t>
   </si>
   <si>
     <t>3</t>
@@ -113,9 +116,6 @@
     <t>14</t>
   </si>
   <si>
-    <t>5</t>
-  </si>
-  <si>
     <t>闪避</t>
   </si>
   <si>
@@ -140,10 +140,10 @@
     <t>9</t>
   </si>
   <si>
-    <t>25</t>
-  </si>
-  <si>
-    <t>抗暴率</t>
+    <t>21</t>
+  </si>
+  <si>
+    <t>暴击</t>
   </si>
   <si>
     <t>12</t>
@@ -1291,23 +1291,23 @@
         <v>22</v>
       </c>
       <c r="I7" s="7" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="J7" s="7" t="s">
         <v>19</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="8" s="2" customFormat="1" customHeight="1" spans="1:11 16381:16383">
       <c r="A8" s="1"/>
       <c r="B8" s="1"/>
       <c r="C8" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E8" s="7" t="s">
         <v>14</v>
@@ -1328,17 +1328,17 @@
         <v>19</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="9" s="2" customFormat="1" customHeight="1" spans="1:11 16381:16383">
       <c r="A9" s="1"/>
       <c r="B9" s="1"/>
       <c r="C9" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E9" s="7" t="s">
         <v>14</v>
@@ -1350,10 +1350,10 @@
         <v>16</v>
       </c>
       <c r="H9" s="7" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="I9" s="7" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="J9" s="7" t="s">
         <v>19</v>
@@ -1366,10 +1366,10 @@
       <c r="A10" s="1"/>
       <c r="B10" s="1"/>
       <c r="C10" s="2" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="E10" s="7" t="s">
         <v>14</v>
@@ -1446,7 +1446,7 @@
         <v>37</v>
       </c>
       <c r="I12" s="7" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="J12" s="7" t="s">
         <v>19</v>
@@ -1477,7 +1477,7 @@
         <v>39</v>
       </c>
       <c r="I13" s="7" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="J13" s="7" t="s">
         <v>19</v>

--- a/Excel/EquipRefineConfig.xlsx
+++ b/Excel/EquipRefineConfig.xlsx
@@ -74,7 +74,7 @@
     <t>20001,20002,20003</t>
   </si>
   <si>
-    <t>4,4,2</t>
+    <t>4,3,2</t>
   </si>
   <si>
     <t>0,30,60</t>

--- a/Excel/EquipRefineConfig.xlsx
+++ b/Excel/EquipRefineConfig.xlsx
@@ -74,7 +74,7 @@
     <t>20001,20002,20003</t>
   </si>
   <si>
-    <t>4,3,2</t>
+    <t>4,2,3</t>
   </si>
   <si>
     <t>0,30,60</t>

--- a/Excel/EquipRefineConfig.xlsx
+++ b/Excel/EquipRefineConfig.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="44">
   <si>
     <t>#</t>
   </si>
@@ -83,70 +83,79 @@
     <t>11</t>
   </si>
   <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>30</t>
+  </si>
+  <si>
+    <t>攻速</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>闪避</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
     <t>10</t>
   </si>
   <si>
-    <t>30</t>
-  </si>
-  <si>
-    <t>攻速</t>
-  </si>
-  <si>
-    <t>2</t>
+    <t>冷却</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>命中</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>24</t>
+  </si>
+  <si>
+    <t>50</t>
+  </si>
+  <si>
+    <t>致命伤害</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>22</t>
+  </si>
+  <si>
+    <t>爆伤</t>
+  </si>
+  <si>
+    <t>9</t>
   </si>
   <si>
     <t>25</t>
   </si>
   <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>抗暴率</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>冷却</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>14</t>
-  </si>
-  <si>
-    <t>闪避</t>
-  </si>
-  <si>
-    <t>13</t>
-  </si>
-  <si>
-    <t>20</t>
-  </si>
-  <si>
-    <t>命中</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>22</t>
-  </si>
-  <si>
-    <t>爆伤</t>
-  </si>
-  <si>
-    <t>9</t>
-  </si>
-  <si>
-    <t>21</t>
-  </si>
-  <si>
-    <t>暴击</t>
+    <t>抗暴</t>
   </si>
   <si>
     <t>12</t>
+  </si>
+  <si>
+    <t>40</t>
   </si>
   <si>
     <t>移速</t>
@@ -1319,7 +1328,7 @@
         <v>16</v>
       </c>
       <c r="H8" s="7" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="I8" s="7" t="s">
         <v>18</v>
@@ -1328,17 +1337,17 @@
         <v>19</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="9" s="2" customFormat="1" customHeight="1" spans="1:11 16381:16383">
       <c r="A9" s="1"/>
       <c r="B9" s="1"/>
       <c r="C9" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E9" s="7" t="s">
         <v>14</v>
@@ -1350,7 +1359,7 @@
         <v>16</v>
       </c>
       <c r="H9" s="7" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I9" s="7" t="s">
         <v>23</v>
@@ -1359,17 +1368,17 @@
         <v>19</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="10" s="2" customFormat="1" customHeight="1" spans="1:11 16381:16383">
       <c r="A10" s="1"/>
       <c r="B10" s="1"/>
       <c r="C10" s="2" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="E10" s="7" t="s">
         <v>14</v>
@@ -1381,26 +1390,26 @@
         <v>16</v>
       </c>
       <c r="H10" s="7" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="I10" s="7" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="J10" s="7" t="s">
         <v>19</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="11" s="2" customFormat="1" customHeight="1" spans="1:11 16381:16383">
       <c r="A11" s="1"/>
       <c r="B11" s="1"/>
       <c r="C11" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="E11" s="7" t="s">
         <v>14</v>
@@ -1412,26 +1421,26 @@
         <v>16</v>
       </c>
       <c r="H11" s="7" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="I11" s="7" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="J11" s="7" t="s">
         <v>19</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="12" s="2" customFormat="1" customHeight="1" spans="1:11 16381:16383">
       <c r="A12" s="1"/>
       <c r="B12" s="1"/>
       <c r="C12" s="2" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E12" s="7" t="s">
         <v>14</v>
@@ -1443,7 +1452,7 @@
         <v>16</v>
       </c>
       <c r="H12" s="7" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="I12" s="7" t="s">
         <v>23</v>
@@ -1452,17 +1461,17 @@
         <v>19</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="13" s="2" customFormat="1" customHeight="1" spans="1:11 16381:16383">
       <c r="A13" s="1"/>
       <c r="B13" s="1"/>
       <c r="C13" s="2" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="E13" s="7" t="s">
         <v>14</v>
@@ -1474,16 +1483,16 @@
         <v>16</v>
       </c>
       <c r="H13" s="7" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="I13" s="7" t="s">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="J13" s="7" t="s">
         <v>19</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
     </row>
     <row r="14" s="1" customFormat="1" customHeight="1" spans="1:11 16381:16383">

--- a/Excel/EquipRefineConfig.xlsx
+++ b/Excel/EquipRefineConfig.xlsx
@@ -1,10 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\legend2\Excel\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView windowHeight="17680"/>
+    <workbookView windowWidth="25600" windowHeight="12080"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="46">
   <si>
     <t>#</t>
   </si>
@@ -134,6 +139,9 @@
     <t>致命伤害</t>
   </si>
   <si>
+    <t>6</t>
+  </si>
+  <si>
     <t>7</t>
   </si>
   <si>
@@ -141,6 +149,9 @@
   </si>
   <si>
     <t>爆伤</t>
+  </si>
+  <si>
+    <t>8</t>
   </si>
   <si>
     <t>9</t>
@@ -1125,7 +1136,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:XFC14"/>
+  <dimension ref="A1:XFC16"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="2" width="9" style="1"/>
@@ -1421,7 +1432,7 @@
         <v>16</v>
       </c>
       <c r="H11" s="7" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="I11" s="7" t="s">
         <v>33</v>
@@ -1430,17 +1441,17 @@
         <v>19</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
     </row>
     <row r="12" s="2" customFormat="1" customHeight="1" spans="1:11 16381:16383">
       <c r="A12" s="1"/>
       <c r="B12" s="1"/>
       <c r="C12" s="2" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E12" s="7" t="s">
         <v>14</v>
@@ -1452,26 +1463,26 @@
         <v>16</v>
       </c>
       <c r="H12" s="7" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="I12" s="7" t="s">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="J12" s="7" t="s">
         <v>19</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="13" s="2" customFormat="1" customHeight="1" spans="1:11 16381:16383">
       <c r="A13" s="1"/>
       <c r="B13" s="1"/>
       <c r="C13" s="2" t="s">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="E13" s="7" t="s">
         <v>14</v>
@@ -1483,28 +1494,90 @@
         <v>16</v>
       </c>
       <c r="H13" s="7" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="I13" s="7" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="J13" s="7" t="s">
         <v>19</v>
       </c>
       <c r="K13" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="14" s="2" customFormat="1" customHeight="1" spans="1:11 16381:16383">
+      <c r="A14" s="1"/>
+      <c r="B14" s="1"/>
+      <c r="C14" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="E14" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="F14" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="G14" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="H14" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="I14" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="J14" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="K14" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="15" s="2" customFormat="1" customHeight="1" spans="1:11 16381:16383">
+      <c r="A15" s="1"/>
+      <c r="B15" s="1"/>
+      <c r="C15" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E15" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="F15" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="G15" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="H15" s="7" t="s">
         <v>43</v>
       </c>
+      <c r="I15" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="J15" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="K15" s="2" t="s">
+        <v>45</v>
+      </c>
     </row>
-    <row r="14" s="1" customFormat="1" customHeight="1" spans="1:11 16381:16383">
-      <c r="E14" s="3"/>
-      <c r="F14" s="3"/>
-      <c r="G14" s="2"/>
-      <c r="H14" s="3"/>
-      <c r="I14" s="3"/>
-      <c r="J14" s="2"/>
-      <c r="XFA14" s="2"/>
-      <c r="XFB14" s="2"/>
-      <c r="XFC14" s="2"/>
+    <row r="16" s="1" customFormat="1" customHeight="1" spans="1:11 16381:16383">
+      <c r="E16" s="3"/>
+      <c r="F16" s="3"/>
+      <c r="G16" s="2"/>
+      <c r="H16" s="3"/>
+      <c r="I16" s="3"/>
+      <c r="J16" s="2"/>
+      <c r="XFA16" s="2"/>
+      <c r="XFB16" s="2"/>
+      <c r="XFC16" s="2"/>
     </row>
   </sheetData>
   <dataValidations count="1">
